--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563017.7022200426</v>
+        <v>563018</v>
       </c>
       <c r="R2" t="n">
-        <v>6295915.228794506</v>
+        <v>6295915</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100251</v>
+        <v>100257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>100258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100258</v>
+        <v>100285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100285</v>
+        <v>100291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100291</v>
+        <v>100298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100298</v>
+        <v>100302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100302</v>
+        <v>100309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100312</v>
+        <v>100317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100317</v>
+        <v>100325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36877-2025 artfynd.xlsx
+++ b/artfynd/A 36877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723972</v>
       </c>
       <c r="B2" t="n">
-        <v>100325</v>
+        <v>100335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
